--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487864_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487864_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.3382</v>
+        <v>1.4534</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9583</v>
+        <v>3.8092</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.62</v>
+        <v>-2.3558</v>
       </c>
       <c r="G2" t="n">
         <v>1.4222</v>
@@ -610,13 +610,13 @@
         <v>1.2487</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3986</v>
+        <v>-0.2835</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.2176</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3301</v>
+        <v>-0.0659</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9340000000000001</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W. BURGOS CABRERA</t>
+          <t>P. FERNANDEZ CHOCARRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3293</v>
+        <v>1.1573</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1036</v>
+        <v>0.489</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2257</v>
+        <v>0.6683</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.185</v>
+        <v>1.3173</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.6674</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2768</v>
+        <v>0.6499</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2806</v>
+        <v>0.75</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9166</v>
+        <v>0.6716</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.636</v>
+        <v>0.0784</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4656</v>
+        <v>0.5674</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8248</v>
+        <v>-0.0041</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3592</v>
+        <v>0.5715</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8325</v>
+        <v>0.6244</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7223</v>
+        <v>-0.2042</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6336</v>
+        <v>-0.261</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0888</v>
+        <v>0.0568</v>
       </c>
       <c r="V3" t="n">
+        <v>-0.5802</v>
+      </c>
+      <c r="W3" t="n">
         <v>0</v>
       </c>
-      <c r="W3" t="n">
-        <v>0.23</v>
-      </c>
       <c r="X3" t="n">
-        <v>-0.23</v>
+        <v>-0.5802</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ CHOCARRO</t>
+          <t>A. CALVO TORRES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8865</v>
+        <v>0.9326</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4237</v>
+        <v>1.3541</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4627</v>
+        <v>-0.4215</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3173</v>
+        <v>2.1701</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6674</v>
+        <v>1.4051</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6499</v>
+        <v>0.765</v>
       </c>
       <c r="J4" t="n">
-        <v>0.75</v>
+        <v>2.1295</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6716</v>
+        <v>1.5115</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0784</v>
+        <v>0.618</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5674</v>
+        <v>0.0407</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0041</v>
+        <v>-0.1063</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5715</v>
+        <v>0.147</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.475</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3262</v>
+        <v>-0.3186</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1487</v>
+        <v>-0.193</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5802</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5802</v>
+        <v>-1.5178</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. CALVO TORRES</t>
+          <t>J. KNOTEK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8036</v>
+        <v>0.3436</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9021</v>
+        <v>3.4491</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0985</v>
+        <v>-3.1055</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1701</v>
+        <v>2.5999</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4051</v>
+        <v>0.1016</v>
       </c>
       <c r="I5" t="n">
-        <v>0.765</v>
+        <v>2.4983</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1295</v>
+        <v>4.8658</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5115</v>
+        <v>1.2695</v>
       </c>
       <c r="L5" t="n">
-        <v>0.618</v>
+        <v>3.5963</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0407</v>
+        <v>-2.2659</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1063</v>
+        <v>-1.1679</v>
       </c>
       <c r="O5" t="n">
-        <v>0.147</v>
+        <v>-1.0981</v>
       </c>
       <c r="P5" t="n">
         <v>0.2081</v>
@@ -844,28 +844,28 @@
         <v>1.2487</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6405999999999999</v>
+        <v>-0.7166</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7705</v>
+        <v>-0.3762</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1299</v>
+        <v>-0.3405</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-1.7477</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5178</v>
+        <v>-1.7477</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. KNOTEK</t>
+          <t>W. BURGOS CABRERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.283</v>
+        <v>0.0037</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6757</v>
+        <v>-0.0752</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.9587</v>
+        <v>0.0789</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5999</v>
+        <v>-0.185</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1016</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4983</v>
+        <v>-0.2768</v>
       </c>
       <c r="J6" t="n">
-        <v>4.8658</v>
+        <v>0.2806</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2695</v>
+        <v>0.9166</v>
       </c>
       <c r="L6" t="n">
-        <v>3.5963</v>
+        <v>-0.636</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.2659</v>
+        <v>-0.4656</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1679</v>
+        <v>-0.8248</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0981</v>
+        <v>0.3592</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2081</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3433</v>
+        <v>0.3968</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1496</v>
+        <v>0.4548</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1937</v>
+        <v>-0.058</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.7477</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7477</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8715000000000001</v>
+        <v>-1.5894</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1176</v>
+        <v>-0.3948</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9891</v>
+        <v>-1.1946</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6546</v>
@@ -1000,13 +1000,13 @@
         <v>1.0406</v>
       </c>
       <c r="S7" t="n">
-        <v>0.944</v>
+        <v>0.2261</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6706</v>
+        <v>0.1582</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2734</v>
+        <v>0.0679</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1203</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0579</v>
+        <v>-2.35</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4444</v>
+        <v>-0.7658</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6135</v>
+        <v>-1.5841</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3756</v>
@@ -1078,13 +1078,13 @@
         <v>0.4162</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1096</v>
+        <v>-0.1825</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.1972</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4091</v>
+        <v>-0.3797</v>
       </c>
       <c r="V8" t="n">
         <v>-1.1675</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.0662</v>
+        <v>-3.2662</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9964</v>
+        <v>-0.4606</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.0698</v>
+        <v>-2.8055</v>
       </c>
       <c r="G9" t="n">
         <v>-1.6427</v>
@@ -1156,13 +1156,13 @@
         <v>0.6244</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8397</v>
+        <v>-0.0396</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5748</v>
+        <v>-0.039</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2649</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>-1.1675</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-10.395</v>
+        <v>-9.3345</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.9527</v>
+        <v>-7.2445</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4424</v>
+        <v>-2.09</v>
       </c>
       <c r="G10" t="n">
         <v>-1.8083</v>
@@ -1234,13 +1234,13 @@
         <v>0.8325</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5482</v>
+        <v>-0.4877</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6277</v>
+        <v>0.0805</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9205</v>
+        <v>-0.5682</v>
       </c>
       <c r="V10" t="n">
         <v>-1.6275</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-11.1606</v>
+        <v>-11.1747</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.6913</v>
+        <v>-8.4117</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4693</v>
+        <v>-2.7629</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7001</v>
@@ -1312,13 +1312,13 @@
         <v>1.2487</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3262</v>
+        <v>0.3122</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3171</v>
+        <v>-0.0376</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6433</v>
+        <v>0.3498</v>
       </c>
       <c r="V11" t="n">
         <v>-1.7513</v>
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-24.4766</v>
+        <v>-23.8242</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.9038</v>
+        <v>-8.251199999999997</v>
       </c>
       <c r="F12" t="n">
-        <v>-15.5729</v>
+        <v>-15.5727</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8567999999999998</v>
+        <v>-0.8568000000000007</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7349999999999999</v>
+        <v>0.7350000000000003</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5919</v>
+        <v>-1.591899999999999</v>
       </c>
       <c r="J12" t="n">
         <v>10.2485</v>
@@ -1390,13 +1390,13 @@
         <v>9.365399999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.1433</v>
+        <v>-1.4906</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0116</v>
+        <v>-0.3593</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1316</v>
+        <v>-1.1314</v>
       </c>
       <c r="V12" t="n">
         <v>-10.03</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.262600000000001</v>
+        <v>7.7229</v>
       </c>
       <c r="E13" t="n">
-        <v>6.4898</v>
+        <v>5.954</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7729</v>
+        <v>1.7689</v>
       </c>
       <c r="G13" t="n">
         <v>2.0152</v>
@@ -1468,13 +1468,13 @@
         <v>3.3299</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7875</v>
+        <v>0.2478</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5153</v>
+        <v>-0.0204</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2721</v>
+        <v>0.2682</v>
       </c>
       <c r="V13" t="n">
         <v>3.3787</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.0289</v>
+        <v>5.2011</v>
       </c>
       <c r="E14" t="n">
         <v>5.1255</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.09660000000000001</v>
+        <v>0.0756</v>
       </c>
       <c r="G14" t="n">
         <v>-0.3477</v>
@@ -1546,13 +1546,13 @@
         <v>2.2893</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3953</v>
+        <v>0.5676</v>
       </c>
       <c r="T14" t="n">
         <v>0.6582</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2629</v>
+        <v>-0.0906</v>
       </c>
       <c r="V14" t="n">
         <v>3.7325</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. ARQUES LOPEZ</t>
+          <t>P. MARIN FONTAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1301</v>
+        <v>3.4029</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1196</v>
+        <v>3.9842</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0106</v>
+        <v>-0.5813</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3793</v>
+        <v>1.4017</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1492</v>
+        <v>-0.1128</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7699</v>
+        <v>1.5145</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6572</v>
+        <v>2.5</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9292</v>
+        <v>0.6672</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.272</v>
+        <v>1.8329</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2779</v>
+        <v>-1.0984</v>
       </c>
       <c r="N15" t="n">
         <v>-0.78</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5021</v>
+        <v>-0.3184</v>
       </c>
       <c r="P15" t="n">
-        <v>2.7055</v>
+        <v>1.4568</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9137</v>
+        <v>1.4568</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1514</v>
+        <v>0.3144</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3295</v>
+        <v>0.0867</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4809</v>
+        <v>0.2277</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1061</v>
+        <v>0.23</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1061</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. OCHI</t>
+          <t>E. ARQUES LOPEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8625</v>
+        <v>2.95</v>
       </c>
       <c r="E16" t="n">
-        <v>1.54</v>
+        <v>0.1196</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3226</v>
+        <v>2.8305</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8602</v>
+        <v>0.3793</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3179</v>
+        <v>1.1492</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1781</v>
+        <v>-0.7699</v>
       </c>
       <c r="J16" t="n">
-        <v>2.0157</v>
+        <v>0.6572</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2702</v>
+        <v>1.9292</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7455</v>
+        <v>-1.272</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1555</v>
+        <v>-0.2779</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5881</v>
+        <v>-0.78</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5674</v>
+        <v>0.5021</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2081</v>
+        <v>2.7055</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2893</v>
+        <v>-0.2081</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4974</v>
+        <v>2.9137</v>
       </c>
       <c r="S16" t="n">
-        <v>2.378</v>
+        <v>-0.0287</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8136</v>
+        <v>-0.3295</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5644</v>
+        <v>0.3008</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5838</v>
+        <v>-0.1061</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5838</v>
+        <v>-0.1061</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. MARIN FONTAN</t>
+          <t>J. GARCIA-ABRIL GUERRERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1973</v>
+        <v>2.0096</v>
       </c>
       <c r="E17" t="n">
-        <v>3.127</v>
+        <v>1.7127</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9297</v>
+        <v>0.2969</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4017</v>
+        <v>-0.9867</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1128</v>
+        <v>-0.6822</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5145</v>
+        <v>-0.3045</v>
       </c>
       <c r="J17" t="n">
-        <v>2.5</v>
+        <v>0.1523</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6672</v>
+        <v>-0.0044</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8329</v>
+        <v>0.1568</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0984</v>
+        <v>-1.1391</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.78</v>
+        <v>-0.6778</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3184</v>
+        <v>-0.4613</v>
       </c>
       <c r="P17" t="n">
-        <v>1.4568</v>
+        <v>1.0406</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4568</v>
+        <v>1.0406</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8912</v>
+        <v>0.5583</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7705</v>
+        <v>0.1629</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1207</v>
+        <v>0.3954</v>
       </c>
       <c r="V17" t="n">
-        <v>0.23</v>
+        <v>1.3975</v>
       </c>
       <c r="W17" t="n">
         <v>1.3975</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. GARCIA-ABRIL GUERRERO</t>
+          <t>I. HANEY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.651</v>
+        <v>1.9515</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8199</v>
+        <v>0.1213</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1689</v>
+        <v>1.8303</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9867</v>
+        <v>-1.6935</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6822</v>
+        <v>-1.0403</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3045</v>
+        <v>-0.6532</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1523</v>
+        <v>-0.0072</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0044</v>
+        <v>0.2214</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1568</v>
+        <v>-0.2286</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1391</v>
+        <v>-1.6863</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6778</v>
+        <v>-1.2617</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4613</v>
+        <v>-0.4245</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0406</v>
+        <v>2.9137</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0406</v>
+        <v>3.1218</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1996</v>
+        <v>-0.0824</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2701</v>
+        <v>-0.4771</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0704</v>
+        <v>0.3948</v>
       </c>
       <c r="V18" t="n">
-        <v>1.3975</v>
+        <v>0.8137</v>
       </c>
       <c r="W18" t="n">
-        <v>1.3975</v>
+        <v>0.8137</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. HANEY</t>
+          <t>M. OCHI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0586</v>
+        <v>1.6275</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6288</v>
+        <v>0.2541</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6874</v>
+        <v>1.3734</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6935</v>
+        <v>0.8602</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0403</v>
+        <v>-0.3179</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6532</v>
+        <v>1.1781</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0072</v>
+        <v>2.0157</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2214</v>
+        <v>0.2702</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.2286</v>
+        <v>1.7455</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6863</v>
+        <v>-1.1555</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2617</v>
+        <v>-0.5881</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4245</v>
+        <v>-0.5674</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9137</v>
+        <v>0.2081</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2081</v>
+        <v>-2.2893</v>
       </c>
       <c r="R19" t="n">
-        <v>3.1218</v>
+        <v>2.4974</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9752999999999999</v>
+        <v>1.143</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2272</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2519</v>
+        <v>0.6153</v>
       </c>
       <c r="V19" t="n">
-        <v>0.8137</v>
+        <v>-0.5838</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="20">
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8125</v>
+        <v>1.0268</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2579</v>
+        <v>0.4722</v>
       </c>
       <c r="F20" t="n">
         <v>0.5545</v>
@@ -2014,10 +2014,10 @@
         <v>0.6244</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2981</v>
+        <v>-0.0838</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1957</v>
+        <v>0.0186</v>
       </c>
       <c r="U20" t="n">
         <v>-0.1024</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. MARTIN MARTIN</t>
+          <t>P. ISERN MAZA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5949</v>
+        <v>0.149</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2465</v>
+        <v>-1.7744</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3484</v>
+        <v>1.9234</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5422</v>
+        <v>-0.3587</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9317</v>
+        <v>-0.6037</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3894</v>
+        <v>0.2449</v>
       </c>
       <c r="J21" t="n">
-        <v>0.107</v>
+        <v>0.5477</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6375999999999999</v>
+        <v>0.2702</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7446</v>
+        <v>0.2776</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6492</v>
+        <v>-0.9065</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.294</v>
+        <v>-0.8738</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3551</v>
+        <v>-0.0326</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0406</v>
+        <v>-2.2893</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6244</v>
+        <v>2.9137</v>
       </c>
       <c r="S21" t="n">
-        <v>1.5534</v>
+        <v>0.1134</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1802</v>
+        <v>-0.0328</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3732</v>
+        <v>0.1462</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. ISERN MAZA</t>
+          <t>P. MARTIN MARTIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1217</v>
+        <v>-0.1361</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5245</v>
+        <v>-0.3964</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4028</v>
+        <v>0.2603</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3587</v>
+        <v>-0.5422</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6037</v>
+        <v>-0.9317</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2449</v>
+        <v>0.3894</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5477</v>
+        <v>0.107</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2702</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2776</v>
+        <v>0.7446</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9065</v>
+        <v>-0.6492</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8738</v>
+        <v>-0.294</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0326</v>
+        <v>-0.3551</v>
       </c>
       <c r="P22" t="n">
+        <v>-0.4162</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-1.0406</v>
+      </c>
+      <c r="R22" t="n">
         <v>0.6244</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-2.2893</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2.9137</v>
-      </c>
       <c r="S22" t="n">
-        <v>-1.1574</v>
+        <v>0.8224</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7829</v>
+        <v>0.5372</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3744</v>
+        <v>0.2851</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>24.4767</v>
+        <v>25.9052</v>
       </c>
       <c r="E23" t="n">
-        <v>15.5729</v>
+        <v>15.5728</v>
       </c>
       <c r="F23" t="n">
-        <v>8.904</v>
+        <v>10.3325</v>
       </c>
       <c r="G23" t="n">
         <v>0.8569</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7352000000000004</v>
+        <v>-0.7352000000000002</v>
       </c>
       <c r="I23" t="n">
         <v>1.592</v>
@@ -2233,7 +2233,7 @@
         <v>-10.2487</v>
       </c>
       <c r="N23" t="n">
-        <v>-7.7788</v>
+        <v>-7.778799999999999</v>
       </c>
       <c r="O23" t="n">
         <v>-2.4696</v>
@@ -2242,19 +2242,19 @@
         <v>11.4466</v>
       </c>
       <c r="Q23" t="n">
-        <v>-9.365299999999998</v>
+        <v>-9.3653</v>
       </c>
       <c r="R23" t="n">
         <v>20.812</v>
       </c>
       <c r="S23" t="n">
-        <v>2.1432</v>
+        <v>3.572</v>
       </c>
       <c r="T23" t="n">
-        <v>1.1316</v>
+        <v>1.1315</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0117</v>
+        <v>2.4405</v>
       </c>
       <c r="V23" t="n">
         <v>10.03</v>
